--- a/data/TTN/最新版班表/TTN_TM.xlsx
+++ b/data/TTN/最新版班表/TTN_TM.xlsx
@@ -1583,9 +1583,9 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>13:16
-NM3511
-21:16
+          <t>12:36
+NM2506
+20:36
 8:00</t>
         </is>
       </c>
@@ -1599,9 +1599,9 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>6:46
-NM1012
-14:46
+          <t>5:26
+NM2001
+13:26
 8:00</t>
         </is>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>I308A</t>
+          <t>E008G</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3925,9 +3925,9 @@
       </c>
       <c r="S21" s="1" t="inlineStr">
         <is>
-          <t>14:30
-STD5
-22:30
+          <t>11:16
+NM0036
+19:16
 8:00</t>
         </is>
       </c>
@@ -4533,9 +4533,9 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>12:36
-NM2506
-20:36
+          <t>13:16
+NM3511
+21:16
 8:00</t>
         </is>
       </c>
@@ -4546,9 +4546,9 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>5:26
-NM2001
-13:26
+          <t>6:46
+NM1012
+14:46
 8:00</t>
         </is>
       </c>
@@ -5953,12 +5953,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>9:04
-NM0027
-17:06
-8:02</t>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>STD</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -12950,12 +12947,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P64" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-NM2009
-14:31
-8:00</t>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="Q64" s="1" t="inlineStr">
@@ -14033,12 +14027,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S69" s="1" t="inlineStr">
-        <is>
-          <t>11:16
-NM0036
-19:16
-8:00</t>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="T69" s="1" t="inlineStr">
@@ -14193,7 +14184,14 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>9:04
+NM0027
+17:06
+8:02</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
@@ -14386,7 +14384,14 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="P74" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
@@ -14525,7 +14530,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
@@ -14664,7 +14676,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
@@ -14724,9 +14743,12 @@
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>NHS1</t>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+PAY1
+24:30
+8:00</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -14749,7 +14771,14 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="O79" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+TTN1
+16:30
+8:00</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>

--- a/data/TTN/最新版班表/TTN_TM.xlsx
+++ b/data/TTN/最新版班表/TTN_TM.xlsx
@@ -1566,9 +1566,9 @@
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>6:46
-NM0012
-14:46
+          <t>5:30
+STD1
+13:30
 8:00</t>
         </is>
       </c>
@@ -1664,34 +1664,34 @@
       </c>
       <c r="Z10" s="1" t="inlineStr">
         <is>
-          <t>7:49
-NM0020
-15:49
+          <t>6:46
+NM0012
+14:46
 8:00</t>
         </is>
       </c>
       <c r="AA10" s="1" t="inlineStr">
         <is>
-          <t>6:51
-NM0013
-14:51
+          <t>6:10
+NM0007
+14:10
 8:00</t>
         </is>
       </c>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>8:30
-OGT2
-17:30
+          <t>6:46
+NM1012
+14:46
 8:00</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>7:49
-NM2020
-15:49
-8:00</t>
+          <t>6:36
+NM1011
+15:11
+8:35</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -6413,9 +6413,9 @@
       </c>
       <c r="L33" s="1" t="inlineStr">
         <is>
-          <t>6:36
-NM0011
-14:36
+          <t>6:46
+NM0012
+14:46
 8:00</t>
         </is>
       </c>
@@ -8563,10 +8563,10 @@
       </c>
       <c r="U43" s="1" t="inlineStr">
         <is>
-          <t>7:01
-NM1014
-15:01
-8:00</t>
+          <t>5:26
+NM0001
+15:06
+9:40</t>
         </is>
       </c>
       <c r="V43" s="1" t="inlineStr">
@@ -10315,9 +10315,9 @@
       </c>
       <c r="AA51" s="1" t="inlineStr">
         <is>
-          <t>6:10
-NM0007
-14:10
+          <t>6:51
+NM0013
+14:51
 8:00</t>
         </is>
       </c>
@@ -10740,9 +10740,9 @@
       </c>
       <c r="AB53" s="1" t="inlineStr">
         <is>
-          <t>6:46
-NM1012
-14:46
+          <t>8:30
+OGT2
+17:30
 8:00</t>
         </is>
       </c>
@@ -11032,6 +11032,221 @@
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
+          <t>15:34
+DO2W
+NM0541
+23:56
+8:22</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>12:46
+NM1521
+22:16
+9:30</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>16:34
+NM0549
+24:38
+8:04</t>
+        </is>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t>15:21
+NM0529
+23:21
+8:00</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>15:04
+NM1536
+23:31
+8:27</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+NM3547
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q55" s="1" t="inlineStr">
+        <is>
+          <t>13:46
+NM3529
+23:11
+9:25</t>
+        </is>
+      </c>
+      <c r="R55" s="1" t="inlineStr">
+        <is>
+          <t>15:21
+NM0530
+23:21
+8:00</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="U55" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+NM0009
+16:06
+9:35</t>
+        </is>
+      </c>
+      <c r="V55" s="1" t="inlineStr">
+        <is>
+          <t>5:26
+NM0003
+15:16
+9:50</t>
+        </is>
+      </c>
+      <c r="W55" s="1" t="inlineStr">
+        <is>
+          <t>12:46
+NM1521
+22:16
+9:30</t>
+        </is>
+      </c>
+      <c r="X55" s="1" t="inlineStr">
+        <is>
+          <t>13:39
+DO2W
+NM2518
+22:11
+8:32</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z55" s="1" t="inlineStr">
+        <is>
+          <t>6:51
+NM0013
+14:51
+8:00</t>
+        </is>
+      </c>
+      <c r="AA55" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+DO3W
+NM0009
+16:06
+9:35</t>
+        </is>
+      </c>
+      <c r="AB55" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+NM0009
+16:06
+9:35</t>
+        </is>
+      </c>
+      <c r="AC55" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+NM1009
+16:06
+9:35</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A022289</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>曾智君</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>15:14
+NM0539
+23:36
+8:22</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>15:31
+NM0536
+23:31
+8:00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>5:46
+NM1002
+15:06
+9:20</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
           <t>13:34
 DO2W
 NM3536
@@ -11039,28 +11254,23 @@
 9:57</t>
         </is>
       </c>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>12:46
-NM1521
-22:16
-9:30</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr">
-        <is>
-          <t>16:34
-NM0549
-24:38
-8:04</t>
-        </is>
-      </c>
-      <c r="M55" s="1" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>15:49
+NM2540
+23:56
+8:07</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>11:36
+NM0034
+19:36
+8:00</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
         <is>
           <t>15:21
 NM0529
@@ -11068,100 +11278,527 @@
 8:00</t>
         </is>
       </c>
-      <c r="N55" s="1" t="inlineStr">
-        <is>
-          <t>15:04
-NM1536
-23:31
-8:27</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-NM3547
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q55" s="1" t="inlineStr">
-        <is>
-          <t>13:46
-NM3529
-23:11
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+LUTS
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>13:16
+NM0512
+21:16
+8:00</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+NM0504
+20:26
+8:12</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+LUTS
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="S56" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+TOWN
+16:30
+8:00</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U56" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+OGT2
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="V56" s="1" t="inlineStr">
+        <is>
+          <t>6:46
+NM1012
+14:46
+8:00</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X56" s="1" t="inlineStr">
+        <is>
+          <t>10:24
+NM5906
+18:36
+8:12</t>
+        </is>
+      </c>
+      <c r="Y56" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+NM0009
+16:26
+9:55</t>
+        </is>
+      </c>
+      <c r="Z56" s="1" t="inlineStr">
+        <is>
+          <t>7:49
+NM0020
+15:49
+8:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB56" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+LUTS
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AC56" s="1" t="inlineStr">
+        <is>
+          <t>5:26
+DO3W
+NM1002
+15:11
+9:45</t>
+        </is>
+      </c>
+      <c r="AD56" s="1" t="inlineStr">
+        <is>
+          <t>5:30
+STD1
+13:30
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A022343</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>黃祥恩</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>11:30
+STD3
+19:30
+8:00</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>11:31
+NM0038
+19:31
+8:00</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>15:21
+NM0529
+23:21
+8:00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>8:24
+NM5903
+16:24
+8:00</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>7:51
+DO2W
+NM0024
+17:16
 9:25</t>
         </is>
       </c>
-      <c r="R55" s="1" t="inlineStr">
-        <is>
-          <t>15:21
-NM0530
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>5:26
+NM1005
+13:26
+8:00</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t>7:24
+NM0018
+15:24
+8:00</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>5:30
+STD1
+13:30
+8:00</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>6:06
+NM0006
+14:06
+8:00</t>
+        </is>
+      </c>
+      <c r="P57" s="1" t="inlineStr">
+        <is>
+          <t>7:31
+NM1019
+16:16
+8:45</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R57" s="1" t="inlineStr">
+        <is>
+          <t>5:51
+NM0005
+13:51
+8:00</t>
+        </is>
+      </c>
+      <c r="S57" s="1" t="inlineStr">
+        <is>
+          <t>5:51
+NM0005
+13:51
+8:00</t>
+        </is>
+      </c>
+      <c r="T57" s="1" t="inlineStr">
+        <is>
+          <t>6:10
+NM0007
+14:10
+8:00</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="V57" s="1" t="inlineStr">
+        <is>
+          <t>14:34
+NM0524
+22:36
+8:02</t>
+        </is>
+      </c>
+      <c r="W57" s="1" t="inlineStr">
+        <is>
+          <t>11:16
+NM1033
+19:16
+8:00</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z57" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AA57" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AC57" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+FAC
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AD57" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+FAC
+17:30
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A022576</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>陳緯宸</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>8:24
+NM1024
+16:31
+8:07</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+STD2
+15:30
+8:00</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>13:39
+NM0518
+22:36
+8:57</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>13:34
+NM0517
+22:11
+8:37</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>14:30
+DO2W
+STD5
+22:30
+8:00</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>13:16
+NM3511
+21:16
+8:00</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>14:34
+NM0543
+24:16
+9:42</t>
+        </is>
+      </c>
+      <c r="M58" s="1" t="inlineStr">
+        <is>
+          <t>15:14
+NM0539
+23:36
+8:22</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>11:56
+NM0034
+19:56
+8:00</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="inlineStr">
+        <is>
+          <t>15:14
+NM1529
 23:21
-8:00</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="U55" s="1" t="inlineStr">
-        <is>
-          <t>5:26
-NM0001
-15:06
-9:40</t>
-        </is>
-      </c>
-      <c r="V55" s="1" t="inlineStr">
-        <is>
-          <t>5:26
-NM0003
-15:16
-9:50</t>
-        </is>
-      </c>
-      <c r="W55" s="1" t="inlineStr">
-        <is>
-          <t>12:46
-NM1521
-22:16
-9:30</t>
-        </is>
-      </c>
-      <c r="X55" s="1" t="inlineStr">
-        <is>
-          <t>13:39
+8:07</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="R58" s="1" t="inlineStr">
+        <is>
+          <t>15:34
+NM1540
+23:56
+8:22</t>
+        </is>
+      </c>
+      <c r="S58" s="1" t="inlineStr">
+        <is>
+          <t>12:36
+NM0506
+20:36
+8:00</t>
+        </is>
+      </c>
+      <c r="T58" s="1" t="inlineStr">
+        <is>
+          <t>13:21
+NM0511
+21:21
+8:00</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="W58" s="1" t="inlineStr">
+        <is>
+          <t>6:21
+NM0008
+14:21
+8:00</t>
+        </is>
+      </c>
+      <c r="X58" s="1" t="inlineStr">
+        <is>
+          <t>5:46
 DO2W
-NM2518
-22:11
-8:32</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z55" s="1" t="inlineStr">
-        <is>
-          <t>6:51
-NM0013
+NM5901
+13:46
+8:00</t>
+        </is>
+      </c>
+      <c r="Y58" s="1" t="inlineStr">
+        <is>
+          <t>6:46
+NM0011
 14:51
-8:00</t>
-        </is>
-      </c>
-      <c r="AA55" s="1" t="inlineStr">
+8:05</t>
+        </is>
+      </c>
+      <c r="Z58" s="1" t="inlineStr">
         <is>
           <t>6:31
 DO3W
@@ -11170,53 +11807,315 @@
 9:35</t>
         </is>
       </c>
-      <c r="AB55" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-NM0009
-16:06
-9:35</t>
-        </is>
-      </c>
-      <c r="AC55" s="1" t="inlineStr">
-        <is>
-          <t>5:26
-NM1002
-15:11
-9:45</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB58" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+OGT2
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AC58" s="1" t="inlineStr">
+        <is>
+          <t>7:49
+NM2020
+15:49
+8:00</t>
+        </is>
+      </c>
+      <c r="AD58" s="1" t="inlineStr">
+        <is>
+          <t>6:21
+NM0008
+14:21
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A022581</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>黃秉洋</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>13:21
+NM0511
+21:21
+8:00</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>12:36
+NM0506
+20:36
+8:00</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>11:39
+NM0034
+20:16
+8:37</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>13:16
+DO2W
+NM1508
+21:16
+8:00</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>15:26
+NM0534
+23:26
+8:00</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t>12:54
+NM0507
+21:06
+8:12</t>
+        </is>
+      </c>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t>15:04
+NM1531
+23:16
+8:12</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>DO2</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S59" s="1" t="inlineStr">
+        <is>
+          <t>15:31
+NM0536
+23:31
+8:00</t>
+        </is>
+      </c>
+      <c r="T59" s="1" t="inlineStr">
+        <is>
+          <t>16:24
+NM0545
+24:26
+8:02</t>
+        </is>
+      </c>
+      <c r="U59" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="V59" s="1" t="inlineStr">
+        <is>
+          <t>16:38
+NM1549
+24:38
+8:00</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AA59" s="1" t="inlineStr">
+        <is>
+          <t>15:21
+NM0529
+23:21
+8:00</t>
+        </is>
+      </c>
+      <c r="AB59" s="1" t="inlineStr">
+        <is>
+          <t>12:11
+NM2501
+20:11
+8:00</t>
+        </is>
+      </c>
+      <c r="AC59" s="1" t="inlineStr">
+        <is>
+          <t>16:38
+NM1549
+24:38
+8:00</t>
+        </is>
+      </c>
+      <c r="AD59" s="1" t="inlineStr">
+        <is>
+          <t>16:26
+NM3545
+24:26
+8:00</t>
+        </is>
+      </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>A022289</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>曾智君</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A022583</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>陳依君</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+NM0504
+20:26
+8:12</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>8:54
+NM0026
+17:16
+8:22</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>15:11
+NM1529
+23:11
+8:00</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>12:36
+NM5905
+20:36
+8:00</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr">
+        <is>
+          <t>15:16
+NM0530
+23:16
+8:00</t>
+        </is>
+      </c>
+      <c r="L60" s="1" t="inlineStr">
         <is>
           <t>15:14
 NM0539
@@ -11224,905 +12123,6 @@
 8:22</t>
         </is>
       </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>15:31
-NM0536
-23:31
-8:00</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H56" s="1" t="inlineStr">
-        <is>
-          <t>5:46
-NM1002
-15:06
-9:20</t>
-        </is>
-      </c>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>15:34
-DO2W
-NM0541
-23:56
-8:22</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>15:49
-NM2540
-23:56
-8:07</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>11:36
-NM0034
-19:36
-8:00</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr">
-        <is>
-          <t>15:21
-NM0529
-23:21
-8:00</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N56" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="P56" s="1" t="inlineStr">
-        <is>
-          <t>13:16
-NM0512
-21:16
-8:00</t>
-        </is>
-      </c>
-      <c r="Q56" s="1" t="inlineStr">
-        <is>
-          <t>12:14
-NM0504
-20:26
-8:12</t>
-        </is>
-      </c>
-      <c r="R56" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S56" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U56" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-OGT2
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V56" s="1" t="inlineStr">
-        <is>
-          <t>6:46
-NM1012
-14:46
-8:00</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X56" s="1" t="inlineStr">
-        <is>
-          <t>10:24
-NM5906
-18:36
-8:12</t>
-        </is>
-      </c>
-      <c r="Y56" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-NM0009
-16:26
-9:55</t>
-        </is>
-      </c>
-      <c r="Z56" s="1" t="inlineStr">
-        <is>
-          <t>6:46
-NM0012
-14:46
-8:00</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB56" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC56" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-DO3W
-NM1009
-16:06
-9:35</t>
-        </is>
-      </c>
-      <c r="AD56" s="1" t="inlineStr">
-        <is>
-          <t>5:30
-STD1
-13:30
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A022343</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>黃祥恩</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>11:30
-STD3
-19:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>11:31
-NM0038
-19:31
-8:00</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>15:21
-NM0529
-23:21
-8:00</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H57" s="1" t="inlineStr">
-        <is>
-          <t>8:24
-NM5903
-16:24
-8:00</t>
-        </is>
-      </c>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>7:51
-DO2W
-NM0024
-17:16
-9:25</t>
-        </is>
-      </c>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>5:26
-NM1005
-13:26
-8:00</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="M57" s="1" t="inlineStr">
-        <is>
-          <t>7:24
-NM0018
-15:24
-8:00</t>
-        </is>
-      </c>
-      <c r="N57" s="1" t="inlineStr">
-        <is>
-          <t>5:30
-STD1
-13:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="inlineStr">
-        <is>
-          <t>6:06
-NM0006
-14:06
-8:00</t>
-        </is>
-      </c>
-      <c r="P57" s="1" t="inlineStr">
-        <is>
-          <t>7:31
-NM1019
-16:16
-8:45</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R57" s="1" t="inlineStr">
-        <is>
-          <t>5:51
-NM0005
-13:51
-8:00</t>
-        </is>
-      </c>
-      <c r="S57" s="1" t="inlineStr">
-        <is>
-          <t>5:51
-NM0005
-13:51
-8:00</t>
-        </is>
-      </c>
-      <c r="T57" s="1" t="inlineStr">
-        <is>
-          <t>6:10
-NM0007
-14:10
-8:00</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="V57" s="1" t="inlineStr">
-        <is>
-          <t>14:34
-NM0524
-22:36
-8:02</t>
-        </is>
-      </c>
-      <c r="W57" s="1" t="inlineStr">
-        <is>
-          <t>11:16
-NM1033
-19:16
-8:00</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AC57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A022576</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>陳緯宸</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>8:24
-NM1024
-16:31
-8:07</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-STD2
-15:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>13:39
-NM0518
-22:36
-8:57</t>
-        </is>
-      </c>
-      <c r="H58" s="1" t="inlineStr">
-        <is>
-          <t>13:34
-NM0517
-22:11
-8:37</t>
-        </is>
-      </c>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>14:30
-DO2W
-STD5
-22:30
-8:00</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>13:16
-NM3511
-21:16
-8:00</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr">
-        <is>
-          <t>14:34
-NM0543
-24:16
-9:42</t>
-        </is>
-      </c>
-      <c r="M58" s="1" t="inlineStr">
-        <is>
-          <t>15:14
-NM0539
-23:36
-8:22</t>
-        </is>
-      </c>
-      <c r="N58" s="1" t="inlineStr">
-        <is>
-          <t>11:56
-NM0034
-19:56
-8:00</t>
-        </is>
-      </c>
-      <c r="O58" s="1" t="inlineStr">
-        <is>
-          <t>15:14
-NM1529
-23:21
-8:07</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R58" s="1" t="inlineStr">
-        <is>
-          <t>15:34
-NM1540
-23:56
-8:22</t>
-        </is>
-      </c>
-      <c r="S58" s="1" t="inlineStr">
-        <is>
-          <t>12:36
-NM0506
-20:36
-8:00</t>
-        </is>
-      </c>
-      <c r="T58" s="1" t="inlineStr">
-        <is>
-          <t>13:21
-NM0511
-21:21
-8:00</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="W58" s="1" t="inlineStr">
-        <is>
-          <t>6:21
-NM0008
-14:21
-8:00</t>
-        </is>
-      </c>
-      <c r="X58" s="1" t="inlineStr">
-        <is>
-          <t>5:46
-DO2W
-NM5901
-13:46
-8:00</t>
-        </is>
-      </c>
-      <c r="Y58" s="1" t="inlineStr">
-        <is>
-          <t>6:46
-NM0011
-14:51
-8:05</t>
-        </is>
-      </c>
-      <c r="Z58" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-DO3W
-NM0009
-16:06
-9:35</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-OGT2
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC58" s="1" t="inlineStr">
-        <is>
-          <t>6:36
-NM1011
-15:11
-8:35</t>
-        </is>
-      </c>
-      <c r="AD58" s="1" t="inlineStr">
-        <is>
-          <t>6:21
-NM0008
-14:21
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A022581</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>黃秉洋</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>13:21
-NM0511
-21:21
-8:00</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>12:36
-NM0506
-20:36
-8:00</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>11:39
-NM0034
-20:16
-8:37</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>13:16
-DO2W
-NM1508
-21:16
-8:00</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>15:26
-NM0534
-23:26
-8:00</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="N59" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t>12:54
-NM0507
-21:06
-8:12</t>
-        </is>
-      </c>
-      <c r="P59" s="1" t="inlineStr">
-        <is>
-          <t>15:04
-NM1531
-23:16
-8:12</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S59" s="1" t="inlineStr">
-        <is>
-          <t>15:31
-NM0536
-23:31
-8:00</t>
-        </is>
-      </c>
-      <c r="T59" s="1" t="inlineStr">
-        <is>
-          <t>16:24
-NM0545
-24:26
-8:02</t>
-        </is>
-      </c>
-      <c r="U59" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V59" s="1" t="inlineStr">
-        <is>
-          <t>16:38
-NM1549
-24:38
-8:00</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AA59" s="1" t="inlineStr">
-        <is>
-          <t>15:21
-NM0529
-23:21
-8:00</t>
-        </is>
-      </c>
-      <c r="AB59" s="1" t="inlineStr">
-        <is>
-          <t>12:11
-NM2501
-20:11
-8:00</t>
-        </is>
-      </c>
-      <c r="AC59" s="1" t="inlineStr">
-        <is>
-          <t>16:38
-NM1549
-24:38
-8:00</t>
-        </is>
-      </c>
-      <c r="AD59" s="1" t="inlineStr">
-        <is>
-          <t>16:26
-NM3545
-24:26
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>A022583</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>陳依君</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>12:14
-NM0504
-20:26
-8:12</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>8:54
-NM0026
-17:16
-8:22</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>15:11
-NM1529
-23:11
-8:00</t>
-        </is>
-      </c>
-      <c r="H60" s="1" t="inlineStr">
-        <is>
-          <t>12:36
-NM5905
-20:36
-8:00</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>15:16
-NM0530
-23:16
-8:00</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr">
-        <is>
-          <t>15:14
-NM0539
-23:36
-8:22</t>
-        </is>
-      </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
           <t>14:16
@@ -12183,10 +12183,10 @@
       </c>
       <c r="U60" s="1" t="inlineStr">
         <is>
-          <t>6:31
-NM0009
-16:06
-9:35</t>
+          <t>7:01
+NM1014
+15:01
+8:00</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -13393,9 +13393,9 @@
       </c>
       <c r="L66" s="1" t="inlineStr">
         <is>
-          <t>5:30
-STD1
-13:30
+          <t>6:36
+NM0011
+14:36
 8:00</t>
         </is>
       </c>
@@ -13444,12 +13444,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S66" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -13515,17 +13512,17 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AD66" s="1" t="inlineStr">
+      <c r="AC66" s="1" t="inlineStr">
         <is>
           <t>8:30
 PAY
 17:30
 8:00</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
